--- a/data/청년정책목록_전처리완료_2025-06-17.xlsx
+++ b/data/청년정책목록_전처리완료_2025-06-17.xlsx
@@ -2951,7 +2951,7 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>경기도 수원시 장안구, 경기도 수원시 권선구, 경기도 수원시 팔달구, 경기도 수원시 영통구, 경기도 의정부시, 경기도 안양시 만안구, 경기도 안양시 동안구, 경기도 부천시 원미구 , 경기도 부천시 소사구 , 경기도 부천시 오정구 , 경기도 광명시, 경기도 평택시, 경기도 동두천시, 경기도 안산시 상록구, 경기도 안산시 단원구, 경기도 과천시, 경기도 구리시, 경기도 남양주시, 경기도 오산시, 경기도 시흥시, 경기도 군포시, 경기도 의왕시, 경기도 하남시, 경기도 용인시 처인구, 경기도 용인시 기흥구, 경기도 용인시 수지구, 경기도 파주시, 경기도 이천시, 경기도 안성시, 경기도 김포시, 경기도 화성시, 경기도 광주시, 경기도 양주시, 경기도 포천시, 경기도 여주시, 경기도 연천군, 경기도 가평군, 경기도 양평군</t>
+          <t>경기도 수원시 장안구, 경기도 수원시 권선구, 경기도 수원시 팔달구, 경기도 수원시 영통구, 경기도 의정부시, 경기도 안양시 만안구, 경기도 안양시 동안구, 경기도 부천시 원미구, 경기도 부천시 소사구, 경기도 부천시 오정구, 경기도 광명시, 경기도 평택시, 경기도 동두천시, 경기도 안산시 상록구, 경기도 안산시 단원구, 경기도 과천시, 경기도 구리시, 경기도 남양주시, 경기도 오산시, 경기도 시흥시, 경기도 군포시, 경기도 의왕시, 경기도 하남시, 경기도 용인시 처인구, 경기도 용인시 기흥구, 경기도 용인시 수지구, 경기도 파주시, 경기도 이천시, 경기도 안성시, 경기도 김포시, 경기도 화성시, 경기도 광주시, 경기도 양주시, 경기도 포천시, 경기도 여주시, 경기도 연천군, 경기도 가평군, 경기도 양평군</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>광주 남구</t>
+          <t>광주광역시 남구</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>광주 남구</t>
+          <t>광주광역시 남구</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>서울 강동구</t>
+          <t>서울특별시 강동구</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>대구 달서구</t>
+          <t>대구광역시 달서구</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>제주 서귀포시</t>
+          <t>제주특별자치도 서귀포시</t>
         </is>
       </c>
       <c r="AG55" t="inlineStr">
@@ -14813,7 +14813,7 @@
       </c>
       <c r="AF86" t="inlineStr">
         <is>
-          <t>부산 남구</t>
+          <t>부산광역시 남구</t>
         </is>
       </c>
       <c r="AG86" t="inlineStr">
@@ -15759,7 +15759,7 @@
       </c>
       <c r="AF92" t="inlineStr">
         <is>
-          <t xml:space="preserve">경기도 부천시 원미구 , 경기도 부천시 소사구 , 경기도 부천시 오정구 </t>
+          <t>경기도 부천시 원미구, 경기도 부천시 소사구, 경기도 부천시 오정구</t>
         </is>
       </c>
       <c r="AG92" t="inlineStr">
@@ -17777,7 +17777,7 @@
       </c>
       <c r="AF104" t="inlineStr">
         <is>
-          <t>서울 금천구</t>
+          <t>서울특별시 금천구</t>
         </is>
       </c>
       <c r="AG104" t="inlineStr">
@@ -30622,7 +30622,7 @@
       </c>
       <c r="AF183" t="inlineStr">
         <is>
-          <t>부산 서구</t>
+          <t>부산광역시 서구</t>
         </is>
       </c>
       <c r="AG183" t="inlineStr">
@@ -31076,7 +31076,7 @@
       </c>
       <c r="AF186" t="inlineStr">
         <is>
-          <t>부산 서구</t>
+          <t>부산광역시 서구</t>
         </is>
       </c>
       <c r="AG186" t="inlineStr">
@@ -31531,7 +31531,7 @@
       </c>
       <c r="AF189" t="inlineStr">
         <is>
-          <t>부산 동구</t>
+          <t>부산광역시 동구</t>
         </is>
       </c>
       <c r="AG189" t="inlineStr">
@@ -32104,7 +32104,7 @@
       </c>
       <c r="AF193" t="inlineStr">
         <is>
-          <t>제주 서귀포시</t>
+          <t>제주특별자치도 서귀포시</t>
         </is>
       </c>
       <c r="AG193" t="inlineStr">
@@ -32690,7 +32690,7 @@
       </c>
       <c r="AF197" t="inlineStr">
         <is>
-          <t>대구 서구</t>
+          <t>대구광역시 서구</t>
         </is>
       </c>
       <c r="AG197" t="inlineStr">
@@ -32838,7 +32838,7 @@
       </c>
       <c r="AF198" t="inlineStr">
         <is>
-          <t>대구 서구</t>
+          <t>대구광역시 서구</t>
         </is>
       </c>
       <c r="AG198" t="inlineStr">
@@ -33009,7 +33009,7 @@
       </c>
       <c r="AF199" t="inlineStr">
         <is>
-          <t>제주 서귀포시</t>
+          <t>제주특별자치도 서귀포시</t>
         </is>
       </c>
       <c r="AG199" t="inlineStr">
@@ -33589,7 +33589,7 @@
       </c>
       <c r="AF203" t="inlineStr">
         <is>
-          <t>인천 남동구</t>
+          <t>인천광역시 남동구</t>
         </is>
       </c>
       <c r="AG203" t="inlineStr">
@@ -33874,7 +33874,7 @@
       </c>
       <c r="AF205" t="inlineStr">
         <is>
-          <t>인천 남동구</t>
+          <t>인천광역시 남동구</t>
         </is>
       </c>
       <c r="AG205" t="inlineStr">
@@ -34586,7 +34586,7 @@
       </c>
       <c r="AF210" t="inlineStr">
         <is>
-          <t>부산 부산진구</t>
+          <t>부산광역시 부산진구</t>
         </is>
       </c>
       <c r="AG210" t="inlineStr">
@@ -34736,7 +34736,7 @@
       </c>
       <c r="AF211" t="inlineStr">
         <is>
-          <t>부산 부산진구</t>
+          <t>부산광역시 부산진구</t>
         </is>
       </c>
       <c r="AG211" t="inlineStr">
@@ -35575,7 +35575,7 @@
       </c>
       <c r="AF216" t="inlineStr">
         <is>
-          <t>부산 사상구</t>
+          <t>부산광역시 사상구</t>
         </is>
       </c>
       <c r="AG216" t="inlineStr">
@@ -35731,7 +35731,7 @@
       </c>
       <c r="AF217" t="inlineStr">
         <is>
-          <t>부산 기장군</t>
+          <t>부산광역시 기장군</t>
         </is>
       </c>
       <c r="AG217" t="inlineStr">
@@ -35891,7 +35891,7 @@
       </c>
       <c r="AF218" t="inlineStr">
         <is>
-          <t>부산 기장군</t>
+          <t>부산광역시 기장군</t>
         </is>
       </c>
       <c r="AG218" t="inlineStr">
@@ -36039,7 +36039,7 @@
       </c>
       <c r="AF219" t="inlineStr">
         <is>
-          <t>부산 영도구</t>
+          <t>부산광역시 영도구</t>
         </is>
       </c>
       <c r="AG219" t="inlineStr">
@@ -36223,7 +36223,7 @@
       </c>
       <c r="AF220" t="inlineStr">
         <is>
-          <t>부산 영도구</t>
+          <t>부산광역시 영도구</t>
         </is>
       </c>
       <c r="AG220" t="inlineStr">
@@ -36373,7 +36373,7 @@
       </c>
       <c r="AF221" t="inlineStr">
         <is>
-          <t>부산 영도구</t>
+          <t>부산광역시 영도구</t>
         </is>
       </c>
       <c r="AG221" t="inlineStr">
@@ -37059,7 +37059,7 @@
       </c>
       <c r="AF225" t="inlineStr">
         <is>
-          <t>부산 금정구</t>
+          <t>부산광역시 금정구</t>
         </is>
       </c>
       <c r="AG225" t="inlineStr">
@@ -37606,7 +37606,7 @@
       </c>
       <c r="AF229" t="inlineStr">
         <is>
-          <t>부산 금정구</t>
+          <t>부산광역시 금정구</t>
         </is>
       </c>
       <c r="AG229" t="inlineStr">
@@ -37742,7 +37742,7 @@
       </c>
       <c r="AF230" t="inlineStr">
         <is>
-          <t>부산 금정구</t>
+          <t>부산광역시 금정구</t>
         </is>
       </c>
       <c r="AG230" t="inlineStr">
@@ -39888,7 +39888,7 @@
       </c>
       <c r="AF245" t="inlineStr">
         <is>
-          <t>부산 연제구</t>
+          <t>부산광역시 연제구</t>
         </is>
       </c>
       <c r="AG245" t="inlineStr">
@@ -42258,7 +42258,7 @@
       </c>
       <c r="AF260" t="inlineStr">
         <is>
-          <t>인천 서구</t>
+          <t>인천광역시 서구</t>
         </is>
       </c>
       <c r="AG260" t="inlineStr">
@@ -43666,7 +43666,7 @@
       </c>
       <c r="AF269" t="inlineStr">
         <is>
-          <t>부산 북구</t>
+          <t>부산광역시 북구</t>
         </is>
       </c>
       <c r="AG269" t="inlineStr">
@@ -43992,7 +43992,7 @@
       </c>
       <c r="AF271" t="inlineStr">
         <is>
-          <t>인천 서구</t>
+          <t>인천광역시 서구</t>
         </is>
       </c>
       <c r="AG271" t="inlineStr">
@@ -44153,7 +44153,7 @@
       </c>
       <c r="AF272" t="inlineStr">
         <is>
-          <t>인천 서구</t>
+          <t>인천광역시 서구</t>
         </is>
       </c>
       <c r="AG272" t="inlineStr">
@@ -45038,7 +45038,7 @@
       </c>
       <c r="AF278" t="inlineStr">
         <is>
-          <t>부산 부산진구</t>
+          <t>부산광역시 부산진구</t>
         </is>
       </c>
       <c r="AG278" t="inlineStr">
@@ -49787,7 +49787,7 @@
       </c>
       <c r="AF309" t="inlineStr">
         <is>
-          <t>울산 동구</t>
+          <t>울산광역시 동구</t>
         </is>
       </c>
       <c r="AG309" t="inlineStr">
@@ -49960,7 +49960,7 @@
       </c>
       <c r="AF310" t="inlineStr">
         <is>
-          <t>울산 동구</t>
+          <t>울산광역시 동구</t>
         </is>
       </c>
       <c r="AG310" t="inlineStr">
@@ -50135,7 +50135,7 @@
       </c>
       <c r="AF311" t="inlineStr">
         <is>
-          <t>울산 동구</t>
+          <t>울산광역시 동구</t>
         </is>
       </c>
       <c r="AG311" t="inlineStr">
@@ -50300,7 +50300,7 @@
       </c>
       <c r="AF312" t="inlineStr">
         <is>
-          <t>부산 사상구</t>
+          <t>부산광역시 사상구</t>
         </is>
       </c>
       <c r="AG312" t="inlineStr">

--- a/data/청년정책목록_전처리완료_2025-06-17.xlsx
+++ b/data/청년정책목록_전처리완료_2025-06-17.xlsx
@@ -982,7 +982,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>대학 졸업</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -4117,7 +4117,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>미취업자, 기타</t>
+          <t>미취업자, 비정규직</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -5649,7 +5649,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>미취업자, 기타</t>
+          <t>미취업자, 비정규직</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -6642,12 +6642,12 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>미취업자, 기타, 기타</t>
+          <t>미취업자, 비정규직, 비정규직</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
@@ -7421,7 +7421,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
@@ -8402,7 +8402,7 @@
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -8695,7 +8695,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -8846,7 +8846,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -8990,7 +8990,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -9161,7 +9161,7 @@
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
@@ -9500,7 +9500,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ53" t="inlineStr">
@@ -9689,7 +9689,7 @@
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
@@ -10699,7 +10699,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
@@ -10865,7 +10865,7 @@
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ61" t="inlineStr">
@@ -11022,7 +11022,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ62" t="inlineStr">
@@ -11179,7 +11179,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ63" t="inlineStr">
@@ -11335,7 +11335,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
@@ -11489,7 +11489,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ65" t="inlineStr">
@@ -11673,7 +11673,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ66" t="inlineStr">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ67" t="inlineStr">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ70" t="inlineStr">
@@ -12480,7 +12480,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
@@ -12787,7 +12787,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
@@ -12944,7 +12944,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
@@ -13097,7 +13097,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ75" t="inlineStr">
@@ -13415,7 +13415,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ77" t="inlineStr">
@@ -13566,7 +13566,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ78" t="inlineStr">
@@ -13891,7 +13891,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ80" t="inlineStr">
@@ -14044,7 +14044,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ81" t="inlineStr">
@@ -14186,7 +14186,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ82" t="inlineStr">
@@ -14337,7 +14337,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ83" t="inlineStr">
@@ -14488,7 +14488,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ84" t="inlineStr">
@@ -14677,7 +14677,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ85" t="inlineStr">
@@ -14828,7 +14828,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
@@ -14981,7 +14981,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ87" t="inlineStr">
@@ -15141,7 +15141,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>고교 재학</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
@@ -15447,7 +15447,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ90" t="inlineStr">
@@ -15595,7 +15595,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ91" t="inlineStr">
@@ -15774,7 +15774,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ92" t="inlineStr">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ93" t="inlineStr">
@@ -16066,7 +16066,7 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ94" t="inlineStr">
@@ -16256,7 +16256,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ95" t="inlineStr">
@@ -16404,7 +16404,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ96" t="inlineStr">
@@ -16588,7 +16588,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
@@ -16746,7 +16746,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ98" t="inlineStr">
@@ -16932,7 +16932,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ99" t="inlineStr">
@@ -17077,7 +17077,7 @@
       </c>
       <c r="AI100" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ100" t="inlineStr">
@@ -17277,7 +17277,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ101" t="inlineStr">
@@ -17438,7 +17438,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ102" t="inlineStr">
@@ -17617,7 +17617,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ103" t="inlineStr">
@@ -17792,7 +17792,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ104" t="inlineStr">
@@ -17930,7 +17930,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ105" t="inlineStr">
@@ -18134,7 +18134,7 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>기타, 기타</t>
+          <t>고교 졸업, 대학 졸업</t>
         </is>
       </c>
       <c r="AJ106" t="inlineStr">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ107" t="inlineStr">
@@ -18440,7 +18440,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ108" t="inlineStr">
@@ -18578,7 +18578,7 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ109" t="inlineStr">
@@ -18759,7 +18759,7 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ110" t="inlineStr">
@@ -19199,7 +19199,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ113" t="inlineStr">
@@ -19348,7 +19348,7 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ114" t="inlineStr">
@@ -19493,7 +19493,7 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ115" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ116" t="inlineStr">
@@ -19790,7 +19790,7 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ117" t="inlineStr">
@@ -19943,7 +19943,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ118" t="inlineStr">
@@ -20094,7 +20094,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ119" t="inlineStr">
@@ -20249,7 +20249,7 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ120" t="inlineStr">
@@ -20403,7 +20403,7 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ121" t="inlineStr">
@@ -20555,7 +20555,7 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ122" t="inlineStr">
@@ -20707,7 +20707,7 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ123" t="inlineStr">
@@ -20866,7 +20866,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ124" t="inlineStr">
@@ -21029,7 +21029,7 @@
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ125" t="inlineStr">
@@ -21179,7 +21179,7 @@
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ126" t="inlineStr">
@@ -21328,7 +21328,7 @@
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ127" t="inlineStr">
@@ -21636,7 +21636,7 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ129" t="inlineStr">
@@ -21798,7 +21798,7 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ130" t="inlineStr">
@@ -21988,7 +21988,7 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ131" t="inlineStr">
@@ -22180,7 +22180,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ132" t="inlineStr">
@@ -22331,7 +22331,7 @@
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ133" t="inlineStr">
@@ -22483,7 +22483,7 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ134" t="inlineStr">
@@ -22775,7 +22775,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ136" t="inlineStr">
@@ -22933,7 +22933,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ137" t="inlineStr">
@@ -23080,7 +23080,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ138" t="inlineStr">
@@ -23237,7 +23237,7 @@
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ139" t="inlineStr">
@@ -23382,7 +23382,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ140" t="inlineStr">
@@ -23535,7 +23535,7 @@
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ141" t="inlineStr">
@@ -23685,7 +23685,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ142" t="inlineStr">
@@ -23842,7 +23842,7 @@
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ143" t="inlineStr">
@@ -24001,7 +24001,7 @@
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ144" t="inlineStr">
@@ -24150,7 +24150,7 @@
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ145" t="inlineStr">
@@ -24300,7 +24300,7 @@
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ146" t="inlineStr">
@@ -24447,7 +24447,7 @@
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ147" t="inlineStr">
@@ -24614,7 +24614,7 @@
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ148" t="inlineStr">
@@ -24759,7 +24759,7 @@
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ149" t="inlineStr">
@@ -24925,7 +24925,7 @@
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ150" t="inlineStr">
@@ -25107,7 +25107,7 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ151" t="inlineStr">
@@ -25281,7 +25281,7 @@
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ152" t="inlineStr">
@@ -25450,7 +25450,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ153" t="inlineStr">
@@ -25614,7 +25614,7 @@
       </c>
       <c r="AI154" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ154" t="inlineStr">
@@ -25785,7 +25785,7 @@
       </c>
       <c r="AI155" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ155" t="inlineStr">
@@ -25951,7 +25951,7 @@
       </c>
       <c r="AI156" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ156" t="inlineStr">
@@ -26116,7 +26116,7 @@
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ157" t="inlineStr">
@@ -26275,7 +26275,7 @@
       </c>
       <c r="AI158" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ158" t="inlineStr">
@@ -26590,7 +26590,7 @@
       </c>
       <c r="AI160" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ160" t="inlineStr">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="AI161" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ161" t="inlineStr">
@@ -26959,7 +26959,7 @@
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ162" t="inlineStr">
@@ -27127,7 +27127,7 @@
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ163" t="inlineStr">
@@ -27313,7 +27313,7 @@
       </c>
       <c r="AI164" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ164" t="inlineStr">
@@ -27484,7 +27484,7 @@
       </c>
       <c r="AI165" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ165" t="inlineStr">
@@ -27637,7 +27637,7 @@
       </c>
       <c r="AI166" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ166" t="inlineStr">
@@ -27808,7 +27808,7 @@
       </c>
       <c r="AI167" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ167" t="inlineStr">
@@ -28005,7 +28005,7 @@
       </c>
       <c r="AI168" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ168" t="inlineStr">
@@ -28157,7 +28157,7 @@
       </c>
       <c r="AI169" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ169" t="inlineStr">
@@ -28347,7 +28347,7 @@
       </c>
       <c r="AI170" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ170" t="inlineStr">
@@ -28520,7 +28520,7 @@
       </c>
       <c r="AI171" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ171" t="inlineStr">
@@ -28688,7 +28688,7 @@
       </c>
       <c r="AI172" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ172" t="inlineStr">
@@ -28858,7 +28858,7 @@
       </c>
       <c r="AI173" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ173" t="inlineStr">
@@ -29009,7 +29009,7 @@
       </c>
       <c r="AI174" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ174" t="inlineStr">
@@ -29215,7 +29215,7 @@
       </c>
       <c r="AI175" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ175" t="inlineStr">
@@ -29393,7 +29393,7 @@
       </c>
       <c r="AI176" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ176" t="inlineStr">
@@ -29608,7 +29608,7 @@
       </c>
       <c r="AI177" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ177" t="inlineStr">
@@ -29795,7 +29795,7 @@
       </c>
       <c r="AI178" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ178" t="inlineStr">
@@ -29985,7 +29985,7 @@
       </c>
       <c r="AI179" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ179" t="inlineStr">
@@ -30161,7 +30161,7 @@
       </c>
       <c r="AI180" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ180" t="inlineStr">
@@ -30323,7 +30323,7 @@
       </c>
       <c r="AI181" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ181" t="inlineStr">
@@ -30486,7 +30486,7 @@
       </c>
       <c r="AI182" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ182" t="inlineStr">
@@ -30637,7 +30637,7 @@
       </c>
       <c r="AI183" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ183" t="inlineStr">
@@ -30781,7 +30781,7 @@
       </c>
       <c r="AI184" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ184" t="inlineStr">
@@ -30942,7 +30942,7 @@
       </c>
       <c r="AI185" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ185" t="inlineStr">
@@ -31091,7 +31091,7 @@
       </c>
       <c r="AI186" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ186" t="inlineStr">
@@ -31231,7 +31231,7 @@
       </c>
       <c r="AI187" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ187" t="inlineStr">
@@ -31546,7 +31546,7 @@
       </c>
       <c r="AI189" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ189" t="inlineStr">
@@ -31688,7 +31688,7 @@
       </c>
       <c r="AI190" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ190" t="inlineStr">
@@ -31830,7 +31830,7 @@
       </c>
       <c r="AI191" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ191" t="inlineStr">
@@ -31969,7 +31969,7 @@
       </c>
       <c r="AI192" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ192" t="inlineStr">
@@ -32119,7 +32119,7 @@
       </c>
       <c r="AI193" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ193" t="inlineStr">
@@ -32274,7 +32274,7 @@
       </c>
       <c r="AI194" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ194" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="AI195" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ195" t="inlineStr">
@@ -32565,7 +32565,7 @@
       </c>
       <c r="AI196" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ196" t="inlineStr">
@@ -32705,7 +32705,7 @@
       </c>
       <c r="AI197" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ197" t="inlineStr">
@@ -32853,7 +32853,7 @@
       </c>
       <c r="AI198" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ198" t="inlineStr">
@@ -33024,7 +33024,7 @@
       </c>
       <c r="AI199" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ199" t="inlineStr">
@@ -33161,7 +33161,7 @@
       </c>
       <c r="AI200" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ200" t="inlineStr">
@@ -33325,7 +33325,7 @@
       </c>
       <c r="AI201" t="inlineStr">
         <is>
-          <t>대학 재학, 기타</t>
+          <t>대학 재학, 대졸 예정</t>
         </is>
       </c>
       <c r="AJ201" t="inlineStr">
@@ -33465,7 +33465,7 @@
       </c>
       <c r="AI202" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ202" t="inlineStr">
@@ -33604,7 +33604,7 @@
       </c>
       <c r="AI203" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ203" t="inlineStr">
@@ -33745,7 +33745,7 @@
       </c>
       <c r="AI204" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ204" t="inlineStr">
@@ -33889,7 +33889,7 @@
       </c>
       <c r="AI205" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ205" t="inlineStr">
@@ -34027,7 +34027,7 @@
       </c>
       <c r="AI206" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ206" t="inlineStr">
@@ -34163,7 +34163,7 @@
       </c>
       <c r="AI207" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ207" t="inlineStr">
@@ -34304,7 +34304,7 @@
       </c>
       <c r="AI208" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ208" t="inlineStr">
@@ -34451,7 +34451,7 @@
       </c>
       <c r="AI209" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ209" t="inlineStr">
@@ -34601,7 +34601,7 @@
       </c>
       <c r="AI210" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ210" t="inlineStr">
@@ -34751,7 +34751,7 @@
       </c>
       <c r="AI211" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ211" t="inlineStr">
@@ -34923,7 +34923,7 @@
       </c>
       <c r="AI212" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ212" t="inlineStr">
@@ -35090,7 +35090,7 @@
       </c>
       <c r="AI213" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ213" t="inlineStr">
@@ -35266,7 +35266,7 @@
       </c>
       <c r="AI214" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>대학 졸업</t>
         </is>
       </c>
       <c r="AJ214" t="inlineStr">
@@ -35444,7 +35444,7 @@
       </c>
       <c r="AI215" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>대학 졸업</t>
         </is>
       </c>
       <c r="AJ215" t="inlineStr">
@@ -35590,7 +35590,7 @@
       </c>
       <c r="AI216" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ216" t="inlineStr">
@@ -35746,7 +35746,7 @@
       </c>
       <c r="AI217" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ217" t="inlineStr">
@@ -35906,7 +35906,7 @@
       </c>
       <c r="AI218" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ218" t="inlineStr">
@@ -36054,7 +36054,7 @@
       </c>
       <c r="AI219" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ219" t="inlineStr">
@@ -36238,7 +36238,7 @@
       </c>
       <c r="AI220" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ220" t="inlineStr">
@@ -36388,7 +36388,7 @@
       </c>
       <c r="AI221" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ221" t="inlineStr">
@@ -36564,7 +36564,7 @@
       </c>
       <c r="AI222" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ222" t="inlineStr">
@@ -36938,7 +36938,7 @@
       </c>
       <c r="AI224" t="inlineStr">
         <is>
-          <t>대학 재학, 기타</t>
+          <t>대학 재학, 대졸 예정</t>
         </is>
       </c>
       <c r="AJ224" t="inlineStr">
@@ -37074,7 +37074,7 @@
       </c>
       <c r="AI225" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ225" t="inlineStr">
@@ -37210,7 +37210,7 @@
       </c>
       <c r="AI226" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ226" t="inlineStr">
@@ -37346,7 +37346,7 @@
       </c>
       <c r="AI227" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ227" t="inlineStr">
@@ -37485,7 +37485,7 @@
       </c>
       <c r="AI228" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ228" t="inlineStr">
@@ -37621,7 +37621,7 @@
       </c>
       <c r="AI229" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ229" t="inlineStr">
@@ -37757,7 +37757,7 @@
       </c>
       <c r="AI230" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ230" t="inlineStr">
@@ -37895,7 +37895,7 @@
       </c>
       <c r="AI231" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ231" t="inlineStr">
@@ -38037,7 +38037,7 @@
       </c>
       <c r="AI232" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ232" t="inlineStr">
@@ -38173,7 +38173,7 @@
       </c>
       <c r="AI233" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ233" t="inlineStr">
@@ -38309,7 +38309,7 @@
       </c>
       <c r="AI234" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ234" t="inlineStr">
@@ -38445,7 +38445,7 @@
       </c>
       <c r="AI235" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ235" t="inlineStr">
@@ -38581,7 +38581,7 @@
       </c>
       <c r="AI236" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ236" t="inlineStr">
@@ -38717,7 +38717,7 @@
       </c>
       <c r="AI237" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ237" t="inlineStr">
@@ -38853,7 +38853,7 @@
       </c>
       <c r="AI238" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ238" t="inlineStr">
@@ -38993,7 +38993,7 @@
       </c>
       <c r="AI239" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ239" t="inlineStr">
@@ -39133,7 +39133,7 @@
       </c>
       <c r="AI240" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ240" t="inlineStr">
@@ -39418,7 +39418,7 @@
       </c>
       <c r="AI242" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ242" t="inlineStr">
@@ -39566,7 +39566,7 @@
       </c>
       <c r="AI243" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ243" t="inlineStr">
@@ -39729,7 +39729,7 @@
       </c>
       <c r="AI244" t="inlineStr">
         <is>
-          <t>기타, 기타</t>
+          <t>대졸 예정, 기타</t>
         </is>
       </c>
       <c r="AJ244" t="inlineStr">
@@ -39903,7 +39903,7 @@
       </c>
       <c r="AI245" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ245" t="inlineStr">
@@ -40054,7 +40054,7 @@
       </c>
       <c r="AI246" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ246" t="inlineStr">
@@ -40201,7 +40201,7 @@
       </c>
       <c r="AI247" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ247" t="inlineStr">
@@ -40357,7 +40357,7 @@
       </c>
       <c r="AI248" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ248" t="inlineStr">
@@ -40493,7 +40493,7 @@
       </c>
       <c r="AI249" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ249" t="inlineStr">
@@ -40646,7 +40646,7 @@
       </c>
       <c r="AI250" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ250" t="inlineStr">
@@ -40807,7 +40807,7 @@
       </c>
       <c r="AI251" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ251" t="inlineStr">
@@ -40968,7 +40968,7 @@
       </c>
       <c r="AI252" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ252" t="inlineStr">
@@ -41127,7 +41127,7 @@
       </c>
       <c r="AI253" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ253" t="inlineStr">
@@ -41300,7 +41300,7 @@
       </c>
       <c r="AI254" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ254" t="inlineStr">
@@ -41477,7 +41477,7 @@
       </c>
       <c r="AI255" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ255" t="inlineStr">
@@ -41641,7 +41641,7 @@
       </c>
       <c r="AI256" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ256" t="inlineStr">
@@ -41818,7 +41818,7 @@
       </c>
       <c r="AI257" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ257" t="inlineStr">
@@ -41975,7 +41975,7 @@
       </c>
       <c r="AI258" t="inlineStr">
         <is>
-          <t>대학 재학, 기타</t>
+          <t>대학 재학, 대학 졸업</t>
         </is>
       </c>
       <c r="AJ258" t="inlineStr">
@@ -42273,7 +42273,7 @@
       </c>
       <c r="AI260" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ260" t="inlineStr">
@@ -42415,7 +42415,7 @@
       </c>
       <c r="AI261" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ261" t="inlineStr">
@@ -42557,7 +42557,7 @@
       </c>
       <c r="AI262" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ262" t="inlineStr">
@@ -42718,7 +42718,7 @@
       </c>
       <c r="AI263" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ263" t="inlineStr">
@@ -42854,7 +42854,7 @@
       </c>
       <c r="AI264" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ264" t="inlineStr">
@@ -43053,7 +43053,7 @@
       </c>
       <c r="AI265" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ265" t="inlineStr">
@@ -43218,7 +43218,7 @@
       </c>
       <c r="AI266" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ266" t="inlineStr">
@@ -43368,7 +43368,7 @@
       </c>
       <c r="AI267" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ267" t="inlineStr">
@@ -43508,7 +43508,7 @@
       </c>
       <c r="AI268" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ268" t="inlineStr">
@@ -43681,7 +43681,7 @@
       </c>
       <c r="AI269" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ269" t="inlineStr">
@@ -44007,7 +44007,7 @@
       </c>
       <c r="AI271" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ271" t="inlineStr">
@@ -44168,7 +44168,7 @@
       </c>
       <c r="AI272" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ272" t="inlineStr">
@@ -44314,7 +44314,7 @@
       </c>
       <c r="AI273" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ273" t="inlineStr">
@@ -44465,7 +44465,7 @@
       </c>
       <c r="AI274" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ274" t="inlineStr">
@@ -44611,7 +44611,7 @@
       </c>
       <c r="AI275" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ275" t="inlineStr">
@@ -44761,7 +44761,7 @@
       </c>
       <c r="AI276" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ276" t="inlineStr">
@@ -44907,7 +44907,7 @@
       </c>
       <c r="AI277" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ277" t="inlineStr">
@@ -45053,7 +45053,7 @@
       </c>
       <c r="AI278" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ278" t="inlineStr">
@@ -45222,7 +45222,7 @@
       </c>
       <c r="AI279" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ279" t="inlineStr">
@@ -45402,7 +45402,7 @@
       </c>
       <c r="AI280" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ280" t="inlineStr">
@@ -45563,7 +45563,7 @@
       </c>
       <c r="AI281" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ281" t="inlineStr">
@@ -45710,7 +45710,7 @@
       </c>
       <c r="AI282" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ282" t="inlineStr">
@@ -45861,7 +45861,7 @@
       </c>
       <c r="AI283" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ283" t="inlineStr">
@@ -46155,7 +46155,7 @@
       </c>
       <c r="AI285" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ285" t="inlineStr">
@@ -46302,7 +46302,7 @@
       </c>
       <c r="AI286" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ286" t="inlineStr">
@@ -46449,7 +46449,7 @@
       </c>
       <c r="AI287" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ287" t="inlineStr">
@@ -46596,7 +46596,7 @@
       </c>
       <c r="AI288" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ288" t="inlineStr">
@@ -46743,7 +46743,7 @@
       </c>
       <c r="AI289" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ289" t="inlineStr">
@@ -46890,7 +46890,7 @@
       </c>
       <c r="AI290" t="inlineStr">
         <is>
-          <t>대학 재학, 기타</t>
+          <t>대학 재학, 대졸 예정</t>
         </is>
       </c>
       <c r="AJ290" t="inlineStr">
@@ -47033,7 +47033,7 @@
       </c>
       <c r="AI291" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ291" t="inlineStr">
@@ -47192,7 +47192,7 @@
       </c>
       <c r="AI292" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ292" t="inlineStr">
@@ -47339,7 +47339,7 @@
       </c>
       <c r="AI293" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ293" t="inlineStr">
@@ -47486,7 +47486,7 @@
       </c>
       <c r="AI294" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ294" t="inlineStr">
@@ -47632,7 +47632,7 @@
       </c>
       <c r="AI295" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ295" t="inlineStr">
@@ -47778,7 +47778,7 @@
       </c>
       <c r="AI296" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ296" t="inlineStr">
@@ -47941,7 +47941,7 @@
       </c>
       <c r="AI297" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>고졸 미만</t>
         </is>
       </c>
       <c r="AJ297" t="inlineStr">
@@ -48081,7 +48081,7 @@
       </c>
       <c r="AI298" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ298" t="inlineStr">
@@ -48229,7 +48229,7 @@
       </c>
       <c r="AI299" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ299" t="inlineStr">
@@ -48377,7 +48377,7 @@
       </c>
       <c r="AI300" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ300" t="inlineStr">
@@ -48537,7 +48537,7 @@
       </c>
       <c r="AI301" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ301" t="inlineStr">
@@ -48692,7 +48692,7 @@
       </c>
       <c r="AI302" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ302" t="inlineStr">
@@ -48823,7 +48823,7 @@
       </c>
       <c r="AI303" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ303" t="inlineStr">
@@ -48975,7 +48975,7 @@
       </c>
       <c r="AI304" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ304" t="inlineStr">
@@ -49097,7 +49097,7 @@
       </c>
       <c r="AI305" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ305" t="inlineStr">
@@ -49279,7 +49279,7 @@
       </c>
       <c r="AI306" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ306" t="inlineStr">
@@ -49458,7 +49458,7 @@
       </c>
       <c r="AI307" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ307" t="inlineStr">
@@ -49628,7 +49628,7 @@
       </c>
       <c r="AI308" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ308" t="inlineStr">
@@ -49797,12 +49797,12 @@
       </c>
       <c r="AH309" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>비정규직</t>
         </is>
       </c>
       <c r="AI309" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ309" t="inlineStr">
@@ -49975,7 +49975,7 @@
       </c>
       <c r="AI310" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ310" t="inlineStr">
@@ -50150,7 +50150,7 @@
       </c>
       <c r="AI311" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ311" t="inlineStr">
@@ -50315,7 +50315,7 @@
       </c>
       <c r="AI312" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ312" t="inlineStr">
@@ -50463,7 +50463,7 @@
       </c>
       <c r="AI313" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ313" t="inlineStr">
@@ -50760,7 +50760,7 @@
       </c>
       <c r="AI315" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ315" t="inlineStr">
@@ -50921,7 +50921,7 @@
       </c>
       <c r="AI316" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ316" t="inlineStr">
@@ -51078,7 +51078,7 @@
       </c>
       <c r="AI317" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ317" t="inlineStr">
@@ -51212,7 +51212,7 @@
       </c>
       <c r="AI318" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ318" t="inlineStr">
@@ -51387,7 +51387,7 @@
       </c>
       <c r="AI319" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ319" t="inlineStr">
@@ -51548,7 +51548,7 @@
       </c>
       <c r="AI320" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ320" t="inlineStr">
@@ -51866,7 +51866,7 @@
       </c>
       <c r="AI322" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ322" t="inlineStr">
@@ -52062,7 +52062,7 @@
       </c>
       <c r="AI323" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ323" t="inlineStr">
@@ -52232,7 +52232,7 @@
       </c>
       <c r="AI324" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ324" t="inlineStr">
@@ -52403,7 +52403,7 @@
       </c>
       <c r="AI325" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ325" t="inlineStr">
@@ -52577,7 +52577,7 @@
       </c>
       <c r="AI326" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ326" t="inlineStr">
@@ -52762,7 +52762,7 @@
       </c>
       <c r="AI327" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ327" t="inlineStr">
@@ -52943,7 +52943,7 @@
       </c>
       <c r="AI328" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>제한없음</t>
         </is>
       </c>
       <c r="AJ328" t="inlineStr">

--- a/data/청년정책목록_전처리완료_2025-06-17.xlsx
+++ b/data/청년정책목록_전처리완료_2025-06-17.xlsx
@@ -2951,7 +2951,7 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>경기도 수원시 장안구, 경기도 수원시 권선구, 경기도 수원시 팔달구, 경기도 수원시 영통구, 경기도 의정부시, 경기도 안양시 만안구, 경기도 안양시 동안구, 경기도 부천시 원미구, 경기도 부천시 소사구, 경기도 부천시 오정구, 경기도 광명시, 경기도 평택시, 경기도 동두천시, 경기도 안산시 상록구, 경기도 안산시 단원구, 경기도 과천시, 경기도 구리시, 경기도 남양주시, 경기도 오산시, 경기도 시흥시, 경기도 군포시, 경기도 의왕시, 경기도 하남시, 경기도 용인시 처인구, 경기도 용인시 기흥구, 경기도 용인시 수지구, 경기도 파주시, 경기도 이천시, 경기도 안성시, 경기도 김포시, 경기도 화성시, 경기도 광주시, 경기도 양주시, 경기도 포천시, 경기도 여주시, 경기도 연천군, 경기도 가평군, 경기도 양평군</t>
+          <t>경기도 수원시 장안구, 경기도 수원시 권선구, 경기도 수원시 팔달구, 경기도 수원시 영통구, 경기도 의정부시, 경기도 안양시 만안구, 경기도 안양시 동안구, 경기도 부천시 원미구 , 경기도 부천시 소사구 , 경기도 부천시 오정구 , 경기도 광명시, 경기도 평택시, 경기도 동두천시, 경기도 안산시 상록구, 경기도 안산시 단원구, 경기도 과천시, 경기도 구리시, 경기도 남양주시, 경기도 오산시, 경기도 시흥시, 경기도 군포시, 경기도 의왕시, 경기도 하남시, 경기도 용인시 처인구, 경기도 용인시 기흥구, 경기도 용인시 수지구, 경기도 파주시, 경기도 이천시, 경기도 안성시, 경기도 김포시, 경기도 화성시, 경기도 광주시, 경기도 양주시, 경기도 포천시, 경기도 여주시, 경기도 연천군, 경기도 가평군, 경기도 양평군</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>미취업자, 비정규직</t>
+          <t>미취업자, 일용근로자</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>제한없음</t>
+          <t>고졸 예정, 고교 졸업, 대졸 예정, 대학 졸업, 석·박사</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>제한없음</t>
+          <t>인문계열, 사회계열, 상경계열, 이학계열, 공학계열, 예체능계열, 농산업계열, 기타</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>광주광역시 남구</t>
+          <t>광주 남구</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>광주광역시 남구</t>
+          <t>광주 남구</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>서울특별시 강동구</t>
+          <t>서울 강동구</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>미취업자, 비정규직</t>
+          <t>미취업자, 단기근로자</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>대구광역시 달서구</t>
+          <t>대구 달서구</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>미취업자, 비정규직, 비정규직</t>
+          <t>미취업자, 일용근로자, 단기근로자</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시</t>
+          <t>제주 서귀포시</t>
         </is>
       </c>
       <c r="AG55" t="inlineStr">
@@ -10041,7 +10041,7 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>제한없음</t>
+          <t>재직자, 자영업자, 일용근로자, 기타</t>
         </is>
       </c>
       <c r="AI56" t="inlineStr">
@@ -10537,7 +10537,7 @@
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>제한없음</t>
+          <t>고교 졸업, 대졸 예정, 대학 졸업</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
@@ -11335,7 +11335,7 @@
       </c>
       <c r="AI64" t="inlineStr">
         <is>
-          <t>제한없음</t>
+          <t>대졸 예정, 대학 졸업, 석·박사</t>
         </is>
       </c>
       <c r="AJ64" t="inlineStr">
@@ -14813,7 +14813,7 @@
       </c>
       <c r="AF86" t="inlineStr">
         <is>
-          <t>부산광역시 남구</t>
+          <t>부산 남구</t>
         </is>
       </c>
       <c r="AG86" t="inlineStr">
@@ -15759,7 +15759,7 @@
       </c>
       <c r="AF92" t="inlineStr">
         <is>
-          <t>경기도 부천시 원미구, 경기도 부천시 소사구, 경기도 부천시 오정구</t>
+          <t xml:space="preserve">경기도 부천시 원미구 , 경기도 부천시 소사구 , 경기도 부천시 오정구 </t>
         </is>
       </c>
       <c r="AG92" t="inlineStr">
@@ -16404,7 +16404,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>제한없음</t>
+          <t>대학 재학, 대졸 예정, 기타</t>
         </is>
       </c>
       <c r="AJ96" t="inlineStr">
@@ -17777,7 +17777,7 @@
       </c>
       <c r="AF104" t="inlineStr">
         <is>
-          <t>서울특별시 금천구</t>
+          <t>서울 금천구</t>
         </is>
       </c>
       <c r="AG104" t="inlineStr">
@@ -19343,7 +19343,7 @@
       </c>
       <c r="AH114" t="inlineStr">
         <is>
-          <t>제한없음</t>
+          <t>재직자, 미취업자, 프리랜서, 일용근로자, 단기근로자, 영농종사자, 기타</t>
         </is>
       </c>
       <c r="AI114" t="inlineStr">
@@ -20398,7 +20398,7 @@
       </c>
       <c r="AH121" t="inlineStr">
         <is>
-          <t>제한없음</t>
+          <t>재직자, 자영업자, 프리랜서, 영농종사자</t>
         </is>
       </c>
       <c r="AI121" t="inlineStr">
@@ -20707,7 +20707,7 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>제한없음</t>
+          <t>대학 재학, 대졸 예정, 대학 졸업, 기타</t>
         </is>
       </c>
       <c r="AJ123" t="inlineStr">
@@ -20866,7 +20866,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>제한없음</t>
+          <t>대학 재학, 대졸 예정, 대학 졸업</t>
         </is>
       </c>
       <c r="AJ124" t="inlineStr">
@@ -21465,7 +21465,7 @@
       </c>
       <c r="AG128" t="inlineStr">
         <is>
-          <t>제한없음</t>
+          <t>인문계열, 사회계열, 상경계열, 이학계열, 공학계열, 예체능계열, 농산업계열, 기타</t>
         </is>
       </c>
       <c r="AH128" t="inlineStr">
@@ -23382,7 +23382,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>제한없음</t>
+          <t>대학 재학, 대졸 예정, 대학 졸업, 석·박사, 기타</t>
         </is>
       </c>
       <c r="AJ140" t="inlineStr">
@@ -23685,7 +23685,7 @@
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>제한없음</t>
+          <t>고졸 예정, 고교 졸업, 대학 재학, 대졸 예정, 대학 졸업, 석·박사, 기타</t>
         </is>
       </c>
       <c r="AJ142" t="inlineStr">
@@ -30622,7 +30622,7 @@
       </c>
       <c r="AF183" t="inlineStr">
         <is>
-          <t>부산광역시 서구</t>
+          <t>부산 서구</t>
         </is>
       </c>
       <c r="AG183" t="inlineStr">
@@ -30781,7 +30781,7 @@
       </c>
       <c r="AI184" t="inlineStr">
         <is>
-          <t>제한없음</t>
+          <t>대학 재학, 대학 졸업, 석·박사</t>
         </is>
       </c>
       <c r="AJ184" t="inlineStr">
@@ -31076,7 +31076,7 @@
       </c>
       <c r="AF186" t="inlineStr">
         <is>
-          <t>부산광역시 서구</t>
+          <t>부산 서구</t>
         </is>
       </c>
       <c r="AG186" t="inlineStr">
@@ -31365,7 +31365,7 @@
       </c>
       <c r="AG188" t="inlineStr">
         <is>
-          <t>제한없음</t>
+          <t>인문계열, 사회계열, 상경계열, 이학계열, 공학계열, 예체능계열, 농산업계열, 기타</t>
         </is>
       </c>
       <c r="AH188" t="inlineStr">
@@ -31531,7 +31531,7 @@
       </c>
       <c r="AF189" t="inlineStr">
         <is>
-          <t>부산광역시 동구</t>
+          <t>부산 동구</t>
         </is>
       </c>
       <c r="AG189" t="inlineStr">
@@ -32104,7 +32104,7 @@
       </c>
       <c r="AF193" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시</t>
+          <t>제주 서귀포시</t>
         </is>
       </c>
       <c r="AG193" t="inlineStr">
@@ -32690,7 +32690,7 @@
       </c>
       <c r="AF197" t="inlineStr">
         <is>
-          <t>대구광역시 서구</t>
+          <t>대구 서구</t>
         </is>
       </c>
       <c r="AG197" t="inlineStr">
@@ -32838,7 +32838,7 @@
       </c>
       <c r="AF198" t="inlineStr">
         <is>
-          <t>대구광역시 서구</t>
+          <t>대구 서구</t>
         </is>
       </c>
       <c r="AG198" t="inlineStr">
@@ -33009,7 +33009,7 @@
       </c>
       <c r="AF199" t="inlineStr">
         <is>
-          <t>제주특별자치도 서귀포시</t>
+          <t>제주 서귀포시</t>
         </is>
       </c>
       <c r="AG199" t="inlineStr">
@@ -33589,7 +33589,7 @@
       </c>
       <c r="AF203" t="inlineStr">
         <is>
-          <t>인천광역시 남동구</t>
+          <t>인천 남동구</t>
         </is>
       </c>
       <c r="AG203" t="inlineStr">
@@ -33874,7 +33874,7 @@
       </c>
       <c r="AF205" t="inlineStr">
         <is>
-          <t>인천광역시 남동구</t>
+          <t>인천 남동구</t>
         </is>
       </c>
       <c r="AG205" t="inlineStr">
@@ -34586,7 +34586,7 @@
       </c>
       <c r="AF210" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구</t>
+          <t>부산 부산진구</t>
         </is>
       </c>
       <c r="AG210" t="inlineStr">
@@ -34736,7 +34736,7 @@
       </c>
       <c r="AF211" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구</t>
+          <t>부산 부산진구</t>
         </is>
       </c>
       <c r="AG211" t="inlineStr">
@@ -35085,7 +35085,7 @@
       </c>
       <c r="AH213" t="inlineStr">
         <is>
-          <t>제한없음</t>
+          <t>재직자, 자영업자, 프리랜서, 일용근로자</t>
         </is>
       </c>
       <c r="AI213" t="inlineStr">
@@ -35575,7 +35575,7 @@
       </c>
       <c r="AF216" t="inlineStr">
         <is>
-          <t>부산광역시 사상구</t>
+          <t>부산 사상구</t>
         </is>
       </c>
       <c r="AG216" t="inlineStr">
@@ -35731,7 +35731,7 @@
       </c>
       <c r="AF217" t="inlineStr">
         <is>
-          <t>부산광역시 기장군</t>
+          <t>부산 기장군</t>
         </is>
       </c>
       <c r="AG217" t="inlineStr">
@@ -35891,7 +35891,7 @@
       </c>
       <c r="AF218" t="inlineStr">
         <is>
-          <t>부산광역시 기장군</t>
+          <t>부산 기장군</t>
         </is>
       </c>
       <c r="AG218" t="inlineStr">
@@ -36039,7 +36039,7 @@
       </c>
       <c r="AF219" t="inlineStr">
         <is>
-          <t>부산광역시 영도구</t>
+          <t>부산 영도구</t>
         </is>
       </c>
       <c r="AG219" t="inlineStr">
@@ -36223,7 +36223,7 @@
       </c>
       <c r="AF220" t="inlineStr">
         <is>
-          <t>부산광역시 영도구</t>
+          <t>부산 영도구</t>
         </is>
       </c>
       <c r="AG220" t="inlineStr">
@@ -36373,7 +36373,7 @@
       </c>
       <c r="AF221" t="inlineStr">
         <is>
-          <t>부산광역시 영도구</t>
+          <t>부산 영도구</t>
         </is>
       </c>
       <c r="AG221" t="inlineStr">
@@ -37059,7 +37059,7 @@
       </c>
       <c r="AF225" t="inlineStr">
         <is>
-          <t>부산광역시 금정구</t>
+          <t>부산 금정구</t>
         </is>
       </c>
       <c r="AG225" t="inlineStr">
@@ -37606,7 +37606,7 @@
       </c>
       <c r="AF229" t="inlineStr">
         <is>
-          <t>부산광역시 금정구</t>
+          <t>부산 금정구</t>
         </is>
       </c>
       <c r="AG229" t="inlineStr">
@@ -37742,7 +37742,7 @@
       </c>
       <c r="AF230" t="inlineStr">
         <is>
-          <t>부산광역시 금정구</t>
+          <t>부산 금정구</t>
         </is>
       </c>
       <c r="AG230" t="inlineStr">
@@ -37752,7 +37752,7 @@
       </c>
       <c r="AH230" t="inlineStr">
         <is>
-          <t>제한없음</t>
+          <t>미취업자, 프리랜서, 일용근로자, 단기근로자, 기타</t>
         </is>
       </c>
       <c r="AI230" t="inlineStr">
@@ -39263,7 +39263,7 @@
       </c>
       <c r="AF241" t="inlineStr">
         <is>
-          <t>경상남도 창원시</t>
+          <t>경상남도 창원시 의창구, 경상남도 창원시 성산구, 경상남도 창원시 마산합포구, 경상남도 창원시 마산회원구, 경상남도 창원시 진해구</t>
         </is>
       </c>
       <c r="AG241" t="inlineStr">
@@ -39403,7 +39403,7 @@
       </c>
       <c r="AF242" t="inlineStr">
         <is>
-          <t>경상남도 창원시</t>
+          <t>경상남도 창원시 의창구, 경상남도 창원시 성산구, 경상남도 창원시 마산합포구, 경상남도 창원시 마산회원구, 경상남도 창원시 진해구</t>
         </is>
       </c>
       <c r="AG242" t="inlineStr">
@@ -39888,7 +39888,7 @@
       </c>
       <c r="AF245" t="inlineStr">
         <is>
-          <t>부산광역시 연제구</t>
+          <t>부산 연제구</t>
         </is>
       </c>
       <c r="AG245" t="inlineStr">
@@ -42258,7 +42258,7 @@
       </c>
       <c r="AF260" t="inlineStr">
         <is>
-          <t>인천광역시 서구</t>
+          <t>인천 서구</t>
         </is>
       </c>
       <c r="AG260" t="inlineStr">
@@ -43666,7 +43666,7 @@
       </c>
       <c r="AF269" t="inlineStr">
         <is>
-          <t>부산광역시 북구</t>
+          <t>부산 북구</t>
         </is>
       </c>
       <c r="AG269" t="inlineStr">
@@ -43676,7 +43676,7 @@
       </c>
       <c r="AH269" t="inlineStr">
         <is>
-          <t>제한없음</t>
+          <t>재직자, 자영업자, 미취업자, 프리랜서, 일용근로자, (예비)창업자, 단기근로자, 영농종사자, 기타</t>
         </is>
       </c>
       <c r="AI269" t="inlineStr">
@@ -43992,7 +43992,7 @@
       </c>
       <c r="AF271" t="inlineStr">
         <is>
-          <t>인천광역시 서구</t>
+          <t>인천 서구</t>
         </is>
       </c>
       <c r="AG271" t="inlineStr">
@@ -44153,7 +44153,7 @@
       </c>
       <c r="AF272" t="inlineStr">
         <is>
-          <t>인천광역시 서구</t>
+          <t>인천 서구</t>
         </is>
       </c>
       <c r="AG272" t="inlineStr">
@@ -44168,7 +44168,7 @@
       </c>
       <c r="AI272" t="inlineStr">
         <is>
-          <t>제한없음</t>
+          <t>고교 졸업, 대졸 예정, 대학 졸업</t>
         </is>
       </c>
       <c r="AJ272" t="inlineStr">
@@ -45038,7 +45038,7 @@
       </c>
       <c r="AF278" t="inlineStr">
         <is>
-          <t>부산광역시 부산진구</t>
+          <t>부산 부산진구</t>
         </is>
       </c>
       <c r="AG278" t="inlineStr">
@@ -49087,17 +49087,17 @@
       </c>
       <c r="AG305" t="inlineStr">
         <is>
-          <t>제한없음</t>
+          <t>인문계열, 사회계열, 상경계열, 이학계열, 공학계열, 예체능계열, 농산업계열</t>
         </is>
       </c>
       <c r="AH305" t="inlineStr">
         <is>
-          <t>제한없음</t>
+          <t>재직자, 자영업자, 미취업자, 프리랜서, 일용근로자, (예비)창업자, 단기근로자, 영농종사자</t>
         </is>
       </c>
       <c r="AI305" t="inlineStr">
         <is>
-          <t>제한없음</t>
+          <t>고졸 미만, 고교 재학, 고졸 예정, 고교 졸업, 대학 재학, 대졸 예정, 대학 졸업, 석·박사</t>
         </is>
       </c>
       <c r="AJ305" t="inlineStr">
@@ -49787,7 +49787,7 @@
       </c>
       <c r="AF309" t="inlineStr">
         <is>
-          <t>울산광역시 동구</t>
+          <t>울산 동구</t>
         </is>
       </c>
       <c r="AG309" t="inlineStr">
@@ -49797,7 +49797,7 @@
       </c>
       <c r="AH309" t="inlineStr">
         <is>
-          <t>비정규직</t>
+          <t>프리랜서</t>
         </is>
       </c>
       <c r="AI309" t="inlineStr">
@@ -49960,7 +49960,7 @@
       </c>
       <c r="AF310" t="inlineStr">
         <is>
-          <t>울산광역시 동구</t>
+          <t>울산 동구</t>
         </is>
       </c>
       <c r="AG310" t="inlineStr">
@@ -50135,7 +50135,7 @@
       </c>
       <c r="AF311" t="inlineStr">
         <is>
-          <t>울산광역시 동구</t>
+          <t>울산 동구</t>
         </is>
       </c>
       <c r="AG311" t="inlineStr">
@@ -50300,7 +50300,7 @@
       </c>
       <c r="AF312" t="inlineStr">
         <is>
-          <t>부산광역시 사상구</t>
+          <t>부산 사상구</t>
         </is>
       </c>
       <c r="AG312" t="inlineStr">
